--- a/config/tables/veteran_camp.xlsx
+++ b/config/tables/veteran_camp.xlsx
@@ -408,13 +408,13 @@
         <v>upgradeCostGrain</v>
       </c>
       <c r="C1" t="str">
-        <v>woundedRatio</v>
+        <v>capacity</v>
       </c>
       <c r="D1" t="str">
-        <v>capacity</v>
+        <v>retentionHours</v>
       </c>
       <c r="E1" t="str">
-        <v>recoverPerHour</v>
+        <v>refundRatio</v>
       </c>
       <c r="F1" t="str">
         <v>unlockEra</v>
@@ -434,7 +434,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -448,13 +448,13 @@
         <v>800</v>
       </c>
       <c r="C3">
-        <v>0.3</v>
+        <v>300</v>
       </c>
       <c r="D3">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -468,13 +468,13 @@
         <v>2400</v>
       </c>
       <c r="C4">
-        <v>0.4</v>
+        <v>600</v>
       </c>
       <c r="D4">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -488,13 +488,13 @@
         <v>6000</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="D5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0.6</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -539,10 +539,10 @@
         <v>营地等级（主键）</v>
       </c>
       <c r="D2" t="str">
-        <v>0,1,2,3…，0=未建/无营地</v>
+        <v>0,1,2,3…，0=未建（无营地=卸兵直接按 refundRatio 即时退款、无暂存/无后悔窗口）</v>
       </c>
       <c r="E2" t="str">
-        <v>标识营地等级；城的营地按其当前等级取对应行</v>
+        <v>城按其营地当前等级取对应行</v>
       </c>
     </row>
     <row r="3">
@@ -556,7 +556,7 @@
         <v>升到本级的粮食成本</v>
       </c>
       <c r="D3" t="str">
-        <v>0 级填 0；如 800 / 2000 …</v>
+        <v>0 级填 0；如 800 / 2400 …</v>
       </c>
       <c r="E3" t="str">
         <v>从上一级升到本级需消耗的粮食</v>
@@ -564,53 +564,53 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>woundedRatio</v>
+        <v>capacity</v>
       </c>
       <c r="B4" t="str">
-        <v>float</v>
+        <v>int</v>
       </c>
       <c r="C4" t="str">
-        <v>阵亡转伤兵比例（0~1）</v>
+        <v>营地容量（暂存兵上限）</v>
       </c>
       <c r="D4" t="str">
-        <v>如 0.35 表示 35% 阵亡变伤兵</v>
+        <v>如 500</v>
       </c>
       <c r="E4" t="str">
-        <v>战斗结算时按此比例把我方阵亡转为伤兵入营（其余真死）</v>
+        <v>营地最多暂存的卸兵数；超出容量的部分按 refundRatio 即时退款、不占位</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>capacity</v>
+        <v>retentionHours</v>
       </c>
       <c r="B5" t="str">
-        <v>int</v>
+        <v>float</v>
       </c>
       <c r="C5" t="str">
-        <v>伤兵容量上限</v>
+        <v>保留时长（小时）</v>
       </c>
       <c r="D5" t="str">
-        <v>如 500</v>
+        <v>如 24 表示一批卸兵 24 小时内线性流失完</v>
       </c>
       <c r="E5" t="str">
-        <v>营地最多容纳的伤兵数，超出的阵亡按真死处理</v>
+        <v>一批卸兵从满到清空所需时间；此期内可原样拉回编队（免再练，但按新兵扣募兵费）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>recoverPerHour</v>
+        <v>refundRatio</v>
       </c>
       <c r="B6" t="str">
-        <v>int</v>
+        <v>float</v>
       </c>
       <c r="C6" t="str">
-        <v>每小时恢复的伤兵数</v>
+        <v>流失退款比例（0~1）</v>
       </c>
       <c r="D6" t="str">
-        <v>如 40</v>
+        <v>默认 0.5=退该兵价值的 50%</v>
       </c>
       <c r="E6" t="str">
-        <v>心跳/worker 每小时把这么多伤兵恢复成该城可用兵</v>
+        <v>每流失一个兵，返还其价值×此比例的粮（这就是原“卸兵退50%粮”的归宿，改成随时间兑现）</v>
       </c>
     </row>
     <row r="7">
@@ -624,7 +624,7 @@
         <v>解锁所需时代</v>
       </c>
       <c r="D7" t="str">
-        <v>如 0 或 2</v>
+        <v>如 0 或 1</v>
       </c>
       <c r="E7" t="str">
         <v>达到此时代才能建造/升到本级</v>
